--- a/JsonConverter/ExcelFiles/WJStage.xlsx
+++ b/JsonConverter/ExcelFiles/WJStage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DD2FF0-82EE-4BFB-9C66-62A05E3ABE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAB044D-F030-4FD0-92A4-B835C0131346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="2130" windowWidth="21270" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6510" yWindow="2415" windowWidth="20730" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WJTable_Stage" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>(name)</t>
   </si>
@@ -75,6 +75,40 @@
   </si>
   <si>
     <t>Wave_1_1,Wave_1_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage_2</t>
+  </si>
+  <si>
+    <t>Stage_3</t>
+  </si>
+  <si>
+    <t>스테이지 2</t>
+  </si>
+  <si>
+    <t>스테이지 3</t>
+  </si>
+  <si>
+    <t>2번 스테이지</t>
+  </si>
+  <si>
+    <t>3번 스테이지</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageCount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NextStageId</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeStageId</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -188,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -198,9 +232,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -431,17 +462,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" customWidth="1"/>
-    <col min="5" max="5" width="42.140625" customWidth="1"/>
+    <col min="3" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="6" width="26.140625" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" customWidth="1"/>
+    <col min="8" max="8" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -449,8 +481,11 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -461,13 +496,22 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1">
+    <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -478,13 +522,22 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -495,290 +548,396 @@
         <v>9</v>
       </c>
       <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4">
         <v>10</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="4">
+        <v>10</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4">
+        <v>10</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
       <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
       <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
       <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
       <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
       <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1">
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
       <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
       <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
       <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-    </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-    </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-    </row>
-    <row r="36" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:5" ht="15.75" customHeight="1"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/WJStage.xlsx
+++ b/JsonConverter/ExcelFiles/WJStage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAB044D-F030-4FD0-92A4-B835C0131346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6C5043-7352-4540-96E6-D5705EDFB445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6510" yWindow="2415" windowWidth="20730" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="750" yWindow="2340" windowWidth="20730" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WJTable_Stage" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>(name)</t>
   </si>
@@ -109,6 +109,14 @@
   </si>
   <si>
     <t>BeforeStageId</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_2_1,Wave_2_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave_3_1,Wave_3_2</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -586,7 +594,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -612,7 +620,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>

--- a/JsonConverter/ExcelFiles/WJStage.xlsx
+++ b/JsonConverter/ExcelFiles/WJStage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6C5043-7352-4540-96E6-D5705EDFB445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEA92B7-57FE-4ADA-AD3F-11178C94F108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="2340" windowWidth="20730" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6195" yWindow="840" windowWidth="22485" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WJTable_Stage" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>(name)</t>
   </si>
@@ -117,6 +117,14 @@
   </si>
   <si>
     <t>Wave_3_1,Wave_3_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RobyBGPath</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D/Chapter_1_BG</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -479,6 +487,7 @@
     <col min="5" max="6" width="26.140625" customWidth="1"/>
     <col min="7" max="7" width="19.140625" customWidth="1"/>
     <col min="8" max="8" width="35.7109375" customWidth="1"/>
+    <col min="9" max="9" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1">
@@ -492,6 +501,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -518,6 +528,9 @@
       <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="I2" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -544,6 +557,9 @@
       <c r="H3" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="I3" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -568,7 +584,9 @@
       <c r="H4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="3"/>
+      <c r="I4" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
@@ -596,7 +614,9 @@
       <c r="H5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1">
@@ -622,7 +642,9 @@
       <c r="H6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="3"/>
+      <c r="I6" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1">
@@ -634,7 +656,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="3"/>
+      <c r="I7" s="4"/>
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1">
@@ -646,7 +668,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="3"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1">
@@ -658,7 +680,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="3"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1">
@@ -670,7 +692,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
-      <c r="I10" s="3"/>
+      <c r="I10" s="6"/>
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1">
@@ -682,7 +704,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
-      <c r="I11" s="3"/>
+      <c r="I11" s="6"/>
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1">
@@ -694,7 +716,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="3"/>
+      <c r="I12" s="5"/>
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1">
@@ -706,7 +728,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
-      <c r="I13" s="3"/>
+      <c r="I13" s="4"/>
       <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1">
@@ -718,7 +740,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
-      <c r="I14" s="3"/>
+      <c r="I14" s="6"/>
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1">
@@ -730,7 +752,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
-      <c r="I15" s="3"/>
+      <c r="I15" s="6"/>
       <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1">
@@ -742,8 +764,9 @@
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -752,8 +775,9 @@
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -762,8 +786,9 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" customHeight="1">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -772,8 +797,9 @@
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" customHeight="1">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -782,8 +808,9 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -792,8 +819,9 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -802,8 +830,9 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -812,8 +841,9 @@
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -822,8 +852,9 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -832,8 +863,9 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -842,8 +874,9 @@
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -852,8 +885,9 @@
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -862,8 +896,9 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -872,8 +907,9 @@
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -882,8 +918,9 @@
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -892,8 +929,9 @@
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
@@ -902,8 +940,9 @@
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I32" s="10"/>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
@@ -912,8 +951,9 @@
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
       <c r="H33" s="10"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I33" s="10"/>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
@@ -922,8 +962,9 @@
       <c r="F34" s="10"/>
       <c r="G34" s="10"/>
       <c r="H34" s="10"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I34" s="10"/>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
@@ -932,20 +973,21 @@
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
       <c r="H35" s="10"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
+      <c r="I35" s="10"/>
+    </row>
+    <row r="36" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/WJStage.xlsx
+++ b/JsonConverter/ExcelFiles/WJStage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEA92B7-57FE-4ADA-AD3F-11178C94F108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25783657-CB3A-4219-8142-811C76141C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6195" yWindow="840" windowWidth="22485" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>(name)</t>
   </si>
@@ -125,6 +125,14 @@
   </si>
   <si>
     <t>2D/Chapter_1_BG</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D/Chapter_2_BG</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D/Chapter_3_BG</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -615,7 +623,7 @@
         <v>24</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -643,7 +651,7 @@
         <v>25</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J6" s="3"/>
     </row>

--- a/JsonConverter/ExcelFiles/WJStage.xlsx
+++ b/JsonConverter/ExcelFiles/WJStage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25783657-CB3A-4219-8142-811C76141C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1F7A1E-CDEC-498B-B463-DADBF9718831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6195" yWindow="840" windowWidth="22485" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="1005" windowWidth="22485" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WJTable_Stage" sheetId="1" r:id="rId1"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>13</v>
@@ -617,7 +617,7 @@
         <v>7</v>
       </c>
       <c r="G5" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>24</v>
@@ -645,7 +645,7 @@
         <v>14</v>
       </c>
       <c r="G6" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>25</v>
